--- a/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_진척율_원본행_입력표_20261027.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_진척율_원본행_입력표_20261027.xlsx
@@ -473,6 +473,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -559,8 +560,8 @@
       <c r="B8" t="n">
         <v>240</v>
       </c>
-      <c r="C8" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -606,7 +607,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6. 담당자는 주 브랜치 `SQ_FM번호_배정대응표_정정본3.csv` 우선(공란은 이전 확정 파일 값) — 일부는 인쇄물 전달 시 담당자와 다릅니다(진행 정리 문서 참고).</t>
+          <t>6. 담당자는 주 브랜치 `SQ_FM번호_배정대응표_정정본3.csv` 기준(사용자 확인 2026-10-27). 정정본3 에 담당자가 없는 4건(SQ NO 129·130·131·214)은 '(미지정)'.</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2859,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>이은주박철호</t>
+          <t>이은주·박철호(공동)</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
@@ -9986,7 +9987,7 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>지성규</t>
+          <t>(미지정)</t>
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr">
@@ -10058,7 +10059,7 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>지성규</t>
+          <t>(미지정)</t>
         </is>
       </c>
       <c r="K131" s="3" t="inlineStr">
@@ -10130,7 +10131,7 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>지성규</t>
+          <t>(미지정)</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
@@ -16106,7 +16107,7 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>박철호</t>
+          <t>(미지정)</t>
         </is>
       </c>
       <c r="K215" s="3" t="inlineStr">

--- a/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_진척율_원본행_입력표_20261027.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/SQ_진척율_원본행_입력표_20261027.xlsx
@@ -473,7 +473,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -561,7 +560,6 @@
         <v>240</v>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -9987,7 +9985,7 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>(미지정)</t>
+          <t>지성규</t>
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr">
@@ -10059,7 +10057,7 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>(미지정)</t>
+          <t>지성규</t>
         </is>
       </c>
       <c r="K131" s="3" t="inlineStr">
@@ -10131,7 +10129,7 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>(미지정)</t>
+          <t>지성규</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
@@ -16107,7 +16105,7 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>(미지정)</t>
+          <t>이광재</t>
         </is>
       </c>
       <c r="K215" s="3" t="inlineStr">
